--- a/ExportExcel/Update User Test.xlsx
+++ b/ExportExcel/Update User Test.xlsx
@@ -41,19 +41,19 @@
     <t>PASSED</t>
   </si>
   <si>
-    <t>178 ms</t>
+    <t>242 ms</t>
   </si>
   <si>
     <t>testUpdateUserIdWithInvalidCharacters</t>
   </si>
   <si>
-    <t>180 ms</t>
+    <t>210 ms</t>
   </si>
   <si>
     <t>testUpdateUserIdWithValidChange</t>
   </si>
   <si>
-    <t>1192 ms</t>
+    <t>802 ms</t>
   </si>
 </sst>
 </file>
